--- a/data/maps/maps.xlsx
+++ b/data/maps/maps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\FFM\data\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A67E67F-B7DB-447B-B01F-D4D54886AEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C71EF8-0310-48ED-BCAA-37F367035F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31200" yWindow="2400" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,172 +381,372 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultColWidth="2.296875" defaultRowHeight="14.1" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="2.296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.1" customHeight="1">
+    <row r="1" spans="1:22" ht="14.1" customHeight="1">
       <c r="A1" s="1">
         <v>2</v>
       </c>
       <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2</v>
+      </c>
+      <c r="U1" s="1">
         <v>3</v>
       </c>
-      <c r="C1" s="1">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V1" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="14.1" customHeight="1">
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="L2" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="14.1" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="L3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="14.1" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="L4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="14.1" customHeight="1">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="L5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="14.1" customHeight="1">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="14.1" customHeight="1">
       <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="L7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="14.1" customHeight="1">
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="14.1" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="L8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="14.1" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="L9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="14.1" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="L10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="14.1" customHeight="1">
+      <c r="V10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="14.1" customHeight="1">
       <c r="A11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="14.1" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="V11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="14.1" customHeight="1">
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>2</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="V12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A13" s="1">
+        <v>2</v>
+      </c>
+      <c r="V13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A14" s="1">
+        <v>2</v>
+      </c>
+      <c r="V14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A15" s="1">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2</v>
+      </c>
+      <c r="V15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A16" s="1">
+        <v>2</v>
+      </c>
+      <c r="V16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A17" s="1">
+        <v>2</v>
+      </c>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A18" s="1">
+        <v>2</v>
+      </c>
+      <c r="V18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="V19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A20" s="1">
+        <v>2</v>
+      </c>
+      <c r="V20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A21" s="1">
+        <v>2</v>
+      </c>
+      <c r="V21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A22" s="1">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>2</v>
+      </c>
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1">
+        <v>2</v>
+      </c>
+      <c r="N22" s="1">
+        <v>2</v>
+      </c>
+      <c r="O22" s="1">
+        <v>2</v>
+      </c>
+      <c r="P22" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>2</v>
+      </c>
+      <c r="R22" s="1">
+        <v>2</v>
+      </c>
+      <c r="S22" s="1">
+        <v>2</v>
+      </c>
+      <c r="T22" s="1">
+        <v>2</v>
+      </c>
+      <c r="U22" s="1">
+        <v>2</v>
+      </c>
+      <c r="V22" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="A17:XFD1048576 A16 K16:XFD16 A9:XFD15 A8 K8:XFD8 A1:XFD7">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>3</formula>
     </cfRule>
